--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N35_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0002T0006Z000C1N35_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.60840189372927</v>
+        <v>4.323865307731007</v>
       </c>
       <c r="D2" t="n">
-        <v>26.34268065682333</v>
+        <v>4.28068560673379</v>
       </c>
       <c r="E2" t="n">
-        <v>12.72868634464878</v>
+        <v>2.068411531005427</v>
       </c>
       <c r="F2" t="n">
-        <v>12.84932675644168</v>
+        <v>2.088015597921772</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>17.55741852634132</v>
+        <v>2.853080510530464</v>
       </c>
       <c r="D3" t="n">
-        <v>17.31100521825884</v>
+        <v>2.813038347967062</v>
       </c>
       <c r="E3" t="n">
-        <v>12.72868634464878</v>
+        <v>2.068411531005427</v>
       </c>
       <c r="F3" t="n">
-        <v>12.84932675644168</v>
+        <v>2.088015597921772</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>10.57508762531955</v>
+        <v>1.718451739114427</v>
       </c>
       <c r="D4" t="n">
-        <v>10.29700571235095</v>
+        <v>1.67326342825703</v>
       </c>
       <c r="E4" t="n">
-        <v>12.72868634464878</v>
+        <v>2.068411531005427</v>
       </c>
       <c r="F4" t="n">
-        <v>12.84932675644168</v>
+        <v>2.088015597921772</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>32.21765545966954</v>
+        <v>5.2353690121963</v>
       </c>
       <c r="D5" t="n">
-        <v>32.13205114485974</v>
+        <v>5.221458311039708</v>
       </c>
       <c r="E5" t="n">
-        <v>12.72868634464878</v>
+        <v>2.068411531005427</v>
       </c>
       <c r="F5" t="n">
-        <v>12.84932675644168</v>
+        <v>2.088015597921772</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>24.13409633767906</v>
+        <v>3.921790654872848</v>
       </c>
       <c r="D6" t="n">
-        <v>24.33116368244199</v>
+        <v>3.953814098396824</v>
       </c>
       <c r="E6" t="n">
-        <v>12.72868634464878</v>
+        <v>2.068411531005427</v>
       </c>
       <c r="F6" t="n">
-        <v>12.84932675644168</v>
+        <v>2.088015597921772</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>37.25693647802837</v>
+        <v>6.054252177679611</v>
       </c>
       <c r="D7" t="n">
-        <v>37.39931683223476</v>
+        <v>6.077388985238149</v>
       </c>
       <c r="E7" t="n">
-        <v>12.72868634464878</v>
+        <v>2.068411531005427</v>
       </c>
       <c r="F7" t="n">
-        <v>12.84932675644168</v>
+        <v>2.088015597921772</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>36.33278670178874</v>
+        <v>5.904077839040671</v>
       </c>
       <c r="D8" t="n">
-        <v>36.523111597334</v>
+        <v>5.935005634566775</v>
       </c>
       <c r="E8" t="n">
-        <v>12.72868634464878</v>
+        <v>2.068411531005427</v>
       </c>
       <c r="F8" t="n">
-        <v>12.84932675644168</v>
+        <v>2.088015597921772</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>53.39770213748873</v>
+        <v>8.677126597341919</v>
       </c>
       <c r="D9" t="n">
-        <v>53.54656486082861</v>
+        <v>8.701316789884649</v>
       </c>
       <c r="E9" t="n">
-        <v>12.72868634464878</v>
+        <v>2.068411531005427</v>
       </c>
       <c r="F9" t="n">
-        <v>12.84932675644168</v>
+        <v>2.088015597921772</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>32.38516649675397</v>
+        <v>5.26258955572252</v>
       </c>
       <c r="D10" t="n">
-        <v>32.65760704158686</v>
+        <v>5.306861144257865</v>
       </c>
       <c r="E10" t="n">
-        <v>12.72868634464878</v>
+        <v>2.068411531005427</v>
       </c>
       <c r="F10" t="n">
-        <v>12.84932675644168</v>
+        <v>2.088015597921772</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>34.47142407378616</v>
+        <v>5.601606411990251</v>
       </c>
       <c r="D11" t="n">
-        <v>34.75477333804472</v>
+        <v>5.647650667432267</v>
       </c>
       <c r="E11" t="n">
-        <v>12.72868634464878</v>
+        <v>2.068411531005427</v>
       </c>
       <c r="F11" t="n">
-        <v>12.84932675644168</v>
+        <v>2.088015597921772</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>39.58227005329041</v>
+        <v>6.432118883659691</v>
       </c>
       <c r="D12" t="n">
-        <v>39.81572558925697</v>
+        <v>6.470055408254258</v>
       </c>
       <c r="E12" t="n">
-        <v>12.72868634464878</v>
+        <v>2.068411531005427</v>
       </c>
       <c r="F12" t="n">
-        <v>12.84932675644168</v>
+        <v>2.088015597921772</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>38.74010744752794</v>
+        <v>6.295267460223291</v>
       </c>
       <c r="D13" t="n">
-        <v>38.86450230311464</v>
+        <v>6.31548162425613</v>
       </c>
       <c r="E13" t="n">
-        <v>12.72868634464878</v>
+        <v>2.068411531005427</v>
       </c>
       <c r="F13" t="n">
-        <v>12.84932675644168</v>
+        <v>2.088015597921772</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>41.98103649254352</v>
+        <v>6.821918430038322</v>
       </c>
       <c r="D14" t="n">
-        <v>42.23921612964816</v>
+        <v>6.863872621067825</v>
       </c>
       <c r="E14" t="n">
-        <v>12.72868634464878</v>
+        <v>2.068411531005427</v>
       </c>
       <c r="F14" t="n">
-        <v>12.84932675644168</v>
+        <v>2.088015597921772</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>49.89788884382844</v>
+        <v>8.108406937122123</v>
       </c>
       <c r="D15" t="n">
-        <v>51.35732090949097</v>
+        <v>8.345564647792283</v>
       </c>
       <c r="E15" t="n">
-        <v>12.72868634464878</v>
+        <v>2.068411531005427</v>
       </c>
       <c r="F15" t="n">
-        <v>12.84932675644168</v>
+        <v>2.088015597921772</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>41.2381917763824</v>
+        <v>6.701206163662141</v>
       </c>
       <c r="D16" t="n">
-        <v>42.16459791396649</v>
+        <v>6.851747161019555</v>
       </c>
       <c r="E16" t="n">
-        <v>12.72868634464878</v>
+        <v>2.068411531005427</v>
       </c>
       <c r="F16" t="n">
-        <v>12.84932675644168</v>
+        <v>2.088015597921772</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>9.586329758622322</v>
+        <v>1.557778585776127</v>
       </c>
       <c r="D17" t="n">
-        <v>9.540298741540331</v>
+        <v>1.550298545500304</v>
       </c>
       <c r="E17" t="n">
-        <v>12.72868634464878</v>
+        <v>2.068411531005427</v>
       </c>
       <c r="F17" t="n">
-        <v>12.84932675644168</v>
+        <v>2.088015597921772</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>37.0185728359814</v>
+        <v>6.015518085846978</v>
       </c>
       <c r="D18" t="n">
-        <v>38.41410970403469</v>
+        <v>6.242292826905636</v>
       </c>
       <c r="E18" t="n">
-        <v>12.72868634464878</v>
+        <v>2.068411531005427</v>
       </c>
       <c r="F18" t="n">
-        <v>12.84932675644168</v>
+        <v>2.088015597921772</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>46.9484331890465</v>
+        <v>7.629120393220056</v>
       </c>
       <c r="D19" t="n">
-        <v>46.97486600241966</v>
+        <v>7.633415725393195</v>
       </c>
       <c r="E19" t="n">
-        <v>12.72868634464878</v>
+        <v>2.068411531005427</v>
       </c>
       <c r="F19" t="n">
-        <v>12.84932675644168</v>
+        <v>2.088015597921772</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>47.83018191644901</v>
+        <v>7.772404561422964</v>
       </c>
       <c r="D20" t="n">
-        <v>47.82084027560819</v>
+        <v>7.770886544786332</v>
       </c>
       <c r="E20" t="n">
-        <v>12.72868634464878</v>
+        <v>2.068411531005427</v>
       </c>
       <c r="F20" t="n">
-        <v>12.84932675644168</v>
+        <v>2.088015597921772</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>28.02781865296216</v>
+        <v>4.554520531106351</v>
       </c>
       <c r="D21" t="n">
-        <v>28.32469698522112</v>
+        <v>4.602763260098431</v>
       </c>
       <c r="E21" t="n">
-        <v>12.72868634464878</v>
+        <v>2.068411531005427</v>
       </c>
       <c r="F21" t="n">
-        <v>12.84932675644168</v>
+        <v>2.088015597921772</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>22.40512248944457</v>
+        <v>3.640832404534743</v>
       </c>
       <c r="D22" t="n">
-        <v>22.02775188953745</v>
+        <v>3.579509682049836</v>
       </c>
       <c r="E22" t="n">
-        <v>12.72868634464878</v>
+        <v>2.068411531005427</v>
       </c>
       <c r="F22" t="n">
-        <v>12.84932675644168</v>
+        <v>2.088015597921772</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>20.81315209275708</v>
+        <v>3.382137215073025</v>
       </c>
       <c r="D23" t="n">
-        <v>20.30779476256961</v>
+        <v>3.300016648917562</v>
       </c>
       <c r="E23" t="n">
-        <v>12.72868634464878</v>
+        <v>2.068411531005427</v>
       </c>
       <c r="F23" t="n">
-        <v>12.84932675644168</v>
+        <v>2.088015597921772</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>35.50685079683589</v>
+        <v>5.769863254485832</v>
       </c>
       <c r="D24" t="n">
-        <v>34.85418766879275</v>
+        <v>5.663805496178822</v>
       </c>
       <c r="E24" t="n">
-        <v>12.72868634464878</v>
+        <v>2.068411531005427</v>
       </c>
       <c r="F24" t="n">
-        <v>12.84932675644168</v>
+        <v>2.088015597921772</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>21.2612186515395</v>
+        <v>3.454948030875169</v>
       </c>
       <c r="D25" t="n">
-        <v>21.89947393028484</v>
+        <v>3.558664513671287</v>
       </c>
       <c r="E25" t="n">
-        <v>12.72868634464878</v>
+        <v>2.068411531005427</v>
       </c>
       <c r="F25" t="n">
-        <v>12.84932675644168</v>
+        <v>2.088015597921772</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>46.61917034060601</v>
+        <v>7.575615180348477</v>
       </c>
       <c r="D26" t="n">
-        <v>46.01581720101253</v>
+        <v>7.477570295164536</v>
       </c>
       <c r="E26" t="n">
-        <v>12.72868634464878</v>
+        <v>2.068411531005427</v>
       </c>
       <c r="F26" t="n">
-        <v>12.84932675644168</v>
+        <v>2.088015597921772</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>4.429793120304661</v>
+        <v>0.7198413820495073</v>
       </c>
       <c r="D27" t="n">
-        <v>5.003356525204883</v>
+        <v>0.8130454353457935</v>
       </c>
       <c r="E27" t="n">
-        <v>12.72868634464878</v>
+        <v>2.068411531005427</v>
       </c>
       <c r="F27" t="n">
-        <v>12.84932675644168</v>
+        <v>2.088015597921772</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
